--- a/data/trans_bre/IP19C08-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP19C08-Clase-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 8,2</t>
+          <t>-4,49; 7,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,59; 11,21</t>
+          <t>-6,18; 11,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,12; 0,0</t>
+          <t>-9,59; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,26; 2,53</t>
+          <t>-8,67; 2,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-80,76; 730,58</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 273,17</t>
+          <t>-100,0; 182,13</t>
         </is>
       </c>
     </row>
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-9,7; 8,11</t>
+          <t>-8,82; 7,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,35; 4,23</t>
+          <t>-6,37; 4,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 11,16</t>
+          <t>-1,05; 10,47</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 7,4</t>
+          <t>-1,11; 7,75</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,34; 1,97</t>
+          <t>-10,13; 1,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 13,23</t>
+          <t>-1,54; 13,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,13; 0,0</t>
+          <t>-14,68; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-11,14; 3,63</t>
+          <t>-9,23; 4,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 9,31</t>
+          <t>0,03; 9,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,47; 2,2</t>
+          <t>-5,96; 2,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,96; 5,24</t>
+          <t>-5,42; 5,05</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-15,08; 1,18</t>
+          <t>-16,19; 1,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-35,09; 1065,59</t>
+          <t>-25,92; 850,84</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 145,8</t>
+          <t>-100,0; 210,61</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-63,06; 186,0</t>
+          <t>-64,96; 170,55</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 189,67</t>
         </is>
       </c>
     </row>
@@ -1060,32 +1060,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 12,85</t>
+          <t>-1,74; 14,11</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,41; 2,51</t>
+          <t>-8,58; 3,23</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,43; 9,95</t>
+          <t>0,07; 9,66</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 5,26</t>
+          <t>-1,12; 6,1</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-48,27; 769,72</t>
+          <t>-46,29; 755,09</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-91,18; 135,87</t>
+          <t>-91,64; 179,26</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1160,27 +1160,27 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-17,08; 2,44</t>
+          <t>-17,43; 3,06</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 11,6</t>
+          <t>-3,37; 11,56</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 9,28</t>
+          <t>-4,68; 7,8</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-7,47; 0,0</t>
+          <t>-7,76; 0,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 79,54</t>
+          <t>-100,0; 141,22</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 4,29</t>
+          <t>-1,57; 4,18</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 2,44</t>
+          <t>-2,42; 2,55</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 3,55</t>
+          <t>-1,09; 3,54</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 0,83</t>
+          <t>-3,99; 0,82</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-28,89; 133,24</t>
+          <t>-25,23; 132,86</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-46,57; 88,34</t>
+          <t>-46,1; 97,93</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-30,46; 204,39</t>
+          <t>-31,81; 190,73</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-76,48; 48,22</t>
+          <t>-76,09; 41,06</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C08-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP19C08-Clase-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 7,04</t>
+          <t>-4,23; 7,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,18; 11,55</t>
+          <t>-6,58; 11,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,59; 0,0</t>
+          <t>-10,12; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,67; 2,56</t>
+          <t>-8,85; 2,33</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-80,79; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 182,13</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,82; 7,68</t>
+          <t>-10,1; 7,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,37; 4,48</t>
+          <t>-6,46; 4,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 10,47</t>
+          <t>-0,91; 10,64</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 7,75</t>
+          <t>-1,3; 7,11</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,13; 1,06</t>
+          <t>-9,99; 1,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 13,28</t>
+          <t>-0,01; 13,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,68; 0,0</t>
+          <t>-14,07; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,23; 4,11</t>
+          <t>-11,27; 3,7</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,03; 9,25</t>
+          <t>-0,0; 9,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,96; 2,15</t>
+          <t>-6,4; 2,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 5,05</t>
+          <t>-4,7; 5,22</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-16,19; 1,38</t>
+          <t>-13,68; 1,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-25,92; 850,84</t>
+          <t>-22,95; 925,12</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 210,61</t>
+          <t>-100,0; 219,57</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-64,96; 170,55</t>
+          <t>-61,56; 216,65</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 189,67</t>
+          <t>-100,0; 211,69</t>
         </is>
       </c>
     </row>
@@ -1060,32 +1060,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 14,11</t>
+          <t>-1,6; 14,18</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,58; 3,23</t>
+          <t>-7,51; 2,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,07; 9,66</t>
+          <t>0,07; 10,05</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 6,1</t>
+          <t>-1,19; 6,36</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-46,29; 755,09</t>
+          <t>-49,01; 840,2</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-91,64; 179,26</t>
+          <t>-88,29; 123,91</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1160,27 +1160,27 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-17,43; 3,06</t>
+          <t>-17,8; 2,95</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 11,56</t>
+          <t>-3,29; 11,69</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 7,8</t>
+          <t>-4,32; 7,88</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-7,76; 0,0</t>
+          <t>-7,44; 0,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 141,22</t>
+          <t>-100,0; 91,07</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 4,18</t>
+          <t>-1,38; 4,09</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 2,55</t>
+          <t>-2,62; 2,42</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 3,54</t>
+          <t>-1,14; 3,33</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 0,82</t>
+          <t>-4,47; 0,92</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-25,23; 132,86</t>
+          <t>-24,16; 114,66</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-46,1; 97,93</t>
+          <t>-48,61; 86,59</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-31,81; 190,73</t>
+          <t>-30,91; 178,57</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-76,09; 41,06</t>
+          <t>-76,77; 48,55</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C08-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP19C08-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-2,92</t>
+          <t>-2,64</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-54,57%</t>
+          <t>-50,22%</t>
         </is>
       </c>
     </row>
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 7,86</t>
+          <t>-4,46; 8,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,58; 11,63</t>
+          <t>-6,59; 11,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,12; 0,0</t>
+          <t>-7,12; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,85; 2,33</t>
+          <t>-7,83; 3,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-80,79; —</t>
+          <t>-80,76; 730,58</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 332,88</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,57</t>
+          <t>2,6</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>228,41%</t>
+          <t>268,19%</t>
         </is>
       </c>
     </row>
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-10,1; 7,72</t>
+          <t>-9,7; 8,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,46; 4,35</t>
+          <t>-7,35; 4,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 10,64</t>
+          <t>-0,95; 11,16</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 7,11</t>
+          <t>-1,04; 7,47</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-1,59</t>
+          <t>-1,9</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-38,16%</t>
+          <t>-48,69%</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,99; 1,57</t>
+          <t>-10,34; 1,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 13,27</t>
+          <t>-0,09; 13,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,07; 0,0</t>
+          <t>-14,13; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-11,27; 3,7</t>
+          <t>-10,99; 2,59</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-3,5</t>
+          <t>-3,81</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-61,52%</t>
+          <t>-63,54%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 9,18</t>
+          <t>-0,61; 9,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,4; 2,54</t>
+          <t>-6,47; 2,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 5,22</t>
+          <t>-4,96; 5,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-13,68; 1,69</t>
+          <t>-16,14; 1,11</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-22,95; 925,12</t>
+          <t>-35,09; 1065,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 219,57</t>
+          <t>-100,0; 145,8</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-61,56; 216,65</t>
+          <t>-63,06; 186,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 211,69</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,16</t>
+          <t>1,3</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>119,39%</t>
+          <t>160,88%</t>
         </is>
       </c>
     </row>
@@ -1060,32 +1060,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 14,18</t>
+          <t>-2,15; 12,85</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,51; 2,39</t>
+          <t>-8,41; 2,51</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,07; 10,05</t>
+          <t>0,43; 9,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 6,36</t>
+          <t>-0,94; 5,79</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-49,01; 840,2</t>
+          <t>-48,27; 769,72</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-88,29; 123,91</t>
+          <t>-91,18; 135,87</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1160,17 +1160,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-17,8; 2,95</t>
+          <t>-17,08; 2,44</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 11,69</t>
+          <t>-3,31; 11,6</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 7,88</t>
+          <t>-4,19; 9,28</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 91,07</t>
+          <t>-100,0; 79,54</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-1,18</t>
+          <t>-1,2</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-34,47%</t>
+          <t>-35,33%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 4,09</t>
+          <t>-1,55; 4,29</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 2,42</t>
+          <t>-2,53; 2,44</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 3,33</t>
+          <t>-0,99; 3,55</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 0,92</t>
+          <t>-4,44; 0,91</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-24,16; 114,66</t>
+          <t>-28,89; 133,24</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-48,61; 86,59</t>
+          <t>-46,57; 88,34</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-30,91; 178,57</t>
+          <t>-30,46; 204,39</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-76,77; 48,55</t>
+          <t>-77,56; 51,65</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C08-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP19C08-Clase-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,175 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>1,29</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2,34</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-1,41</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-2,64</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>46,6%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>42,69%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-50,22%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>1.286722192516309</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>2.343154887948013</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-1.41185287042453</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-2.639916114624565</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.4659902243138943</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.4269434442899263</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-0.502232064415589</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-4,46; 8,2</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-6,59; 11,21</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-7,12; 0,0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-7,83; 3,06</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-80,76; 730,58</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 332,88</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-4.462399077694252</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-6.592411457015102</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-7.124364182362536</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-7.834886495880516</v>
+      </c>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="n">
+        <v>-0.8076374452983315</v>
+      </c>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>8.197981282318047</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>11.20502373858994</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>3.055937093071599</v>
+      </c>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="n">
+        <v>7.305768041199201</v>
+      </c>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="n">
+        <v>3.32876369479226</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Grupo III</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-1,29</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-1,11</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>3,31</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2,6</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-19,23%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-29,44%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>311,09%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>268,19%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-9,7; 8,11</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-7,35; 4,23</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-0,95; 11,16</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-1,04; 7,47</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-1.285983644350753</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-1.11453535410058</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>3.31327801119389</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>2.604220463520001</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.1923493214753641</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.2943780264737011</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>3.110917520382286</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>2.681884557817698</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Grupo IV y V</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-3,56</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>4,95</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-4,08</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-1,9</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-70,05%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>310,92%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-48,69%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-9.697138649747849</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-7.34501312922335</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-0.9474293033537843</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-1.040769034659919</v>
+      </c>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
+      <c r="I8" s="6" t="inlineStr"/>
+      <c r="J8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-10,34; 1,97</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-0,09; 13,23</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-14,13; 0,0</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-10,99; 2,59</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>8.112171504646959</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>4.226304095254303</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>11.16337777738237</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>7.466765386226457</v>
+      </c>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
+      <c r="I9" s="6" t="inlineStr"/>
+      <c r="J9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Grupo VI</t>
+          <t>Grupo IV y V</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,299 +795,179 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>4,4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-1,81</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-0,04</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-3,81</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>166,1%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-41,99%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-0,64%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-63,54%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-3.562674443926535</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>4.951175708401568</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-4.078746724006827</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-1.896266530937139</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.7004714391854497</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>3.109235281853528</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.4868729471991427</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-0,61; 9,31</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-6,47; 2,2</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-4,96; 5,24</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-16,14; 1,11</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-35,09; 1065,59</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 145,8</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-63,06; 186,0</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-10.33686757857399</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-0.08593366875001236</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-14.13489873772024</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-10.98934732649697</v>
+      </c>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr"/>
+      <c r="I11" s="6" t="inlineStr"/>
+      <c r="J11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Grupo VII</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>1.96731607869816</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>13.22549000236697</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>2.592055962408132</v>
+      </c>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+      <c r="I12" s="6" t="inlineStr"/>
+      <c r="J12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>5,31</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-2,27</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>4,09</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,3</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>127,51%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-41,35%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>443,63%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>160,88%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-2,15; 12,85</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-8,41; 2,51</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0,43; 9,95</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-0,94; 5,79</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-48,27; 769,72</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-91,18; 135,87</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C13" s="5" t="n">
+        <v>4.403306867000426</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-1.811773500907582</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-0.03520584840804655</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-3.807420335300592</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>1.66097816521267</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.4199202373176181</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.006368171555902439</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.6354408299971441</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>No ha trabajado</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>-6,31</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>1,24</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>1,73</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-1,49</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-54,97%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>74,55%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>85,52%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-0.6110850811809959</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-6.467515725644366</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-4.955383012190513</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-16.13669799530045</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.3509268438754525</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.6305933132625826</v>
+      </c>
+      <c r="J14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>-17,08; 2,44</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>-3,31; 11,6</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>-4,19; 9,28</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>-7,44; 0,0</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 79,54</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>9.312667482688525</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>2.204565400915921</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>5.238838444334165</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>1.10645023077334</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>10.65593459124062</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>1.457951876734279</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>1.860020260926223</v>
+      </c>
+      <c r="J15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Grupo VII</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1210,97 +975,277 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>1,2</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-0,02</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1,07</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-1,2</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>25,34%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-0,57%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>38,18%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>-35,33%</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>5.308474020484486</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-2.274119357538857</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>4.087629118448068</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>1.302220549910081</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>1.275077735441192</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.4134788901245059</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>4.436329193617736</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>1.608756128426611</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-1,55; 4,29</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-2,53; 2,44</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-0,99; 3,55</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-4,44; 0,91</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-28,89; 133,24</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-46,57; 88,34</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-30,46; 204,39</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-77,56; 51,65</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-2.147124081831926</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-8.410729987757987</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.433858162075205</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-0.9435345184644226</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.4826628332242621</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.9118252897080258</v>
+      </c>
+      <c r="I17" s="6" t="inlineStr"/>
+      <c r="J17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>12.85237835628582</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>2.511591000967811</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>9.949616924078491</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>5.78931875411007</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>7.69724225843502</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>1.358710318216293</v>
+      </c>
+      <c r="I18" s="6" t="inlineStr"/>
+      <c r="J18" s="6" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>-6.311427850710785</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>1.241737010673354</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>1.732069101851601</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>-1.487872861863151</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-0.5496823047693418</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>0.745476788627825</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>0.8552198729204664</v>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>-17.07737353477116</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>-3.305886660773196</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>-4.187318797103223</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>-7.437290305010426</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H20" s="6" t="inlineStr"/>
+      <c r="I20" s="6" t="inlineStr"/>
+      <c r="J20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>2.443485714957229</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>11.60040574986611</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>9.282430368024624</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0.7954181713327166</v>
+      </c>
+      <c r="H21" s="6" t="inlineStr"/>
+      <c r="I21" s="6" t="inlineStr"/>
+      <c r="J21" s="6" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>1.195447008821343</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-0.02303004708019765</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>1.066832009674765</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>-1.204358251822283</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>0.2533773340987567</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>-0.005726496365971683</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>0.3818380011838161</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>-0.3533071162550028</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-1.549645005603802</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-2.525915379806751</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-0.9876579832968169</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-4.43836624792476</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>-0.2889043827715341</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>-0.4657359017836696</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>-0.3046118686009944</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>-0.7755535052564966</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>4.289514841501173</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>2.436828408296897</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>3.546473886735227</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>0.9077839636363164</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>1.33235906573919</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>0.8834056909928533</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>2.0439208070302</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>0.5165212698795589</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1308,16 +1253,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
